--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8652" uniqueCount="716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8652" uniqueCount="715">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-19T14:28:10+00:00</t>
+    <t>2023-01-20T17:48:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,7 +102,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/StructureDefinition/CorePacienteCl</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/CorePacienteCl</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -439,7 +439,7 @@
     <t>nacionalidad</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7chile.cl/fhir/ig/corecl/StructureDefinition/CodigoPaises}
+    <t xml:space="preserve">Extension {https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/CodigoPaises}
 </t>
   </si>
   <si>
@@ -641,7 +641,7 @@
     <t>Value Set de Tipos de Documentos y CI Nacionales</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/VSTiposDocumentos</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSTiposDocumentos</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1261,9 +1261,6 @@
     <t>Nombre Social</t>
   </si>
   <si>
-    <t>Nombre Social del Paciente</t>
-  </si>
-  <si>
     <t>Patient.telecom</t>
   </si>
   <si>
@@ -1546,7 +1543,7 @@
     <t>Patient.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7chile.cl/fhir/ig/corecl/StructureDefinition/cl-address}
+    <t xml:space="preserve">Address {https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/cl-address}
 </t>
   </si>
   <si>
@@ -1683,7 +1680,7 @@
     <t>IdContacto</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7chile.cl/fhir/ig/corecl/StructureDefinition/IdContacto}
+    <t xml:space="preserve">Extension {https://hl7chile.cl/fhir/ig/CoreCL/StructureDefinition/IdContacto}
 </t>
   </si>
   <si>
@@ -1982,7 +1979,7 @@
     <t>Value Set de HL7, # de elementos es muy grande para poder visualizarlo</t>
   </si>
   <si>
-    <t>https://hl7chile.cl/fhir/ig/corecl/ValueSet/VSCodigoslenguaje</t>
+    <t>https://hl7chile.cl/fhir/ig/CoreCL/ValueSet/VSCodigoslenguaje</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -2567,7 +2564,7 @@
     <col min="22" max="22" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="71.51171875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="57.28125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="58.3359375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="77.02734375" customWidth="true" bestFit="true"/>
@@ -14492,7 +14489,7 @@
         <v>401</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="M105" t="s" s="2">
         <v>369</v>
@@ -14915,7 +14912,7 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" t="s" s="2">
@@ -14938,19 +14935,19 @@
         <v>83</v>
       </c>
       <c r="J109" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K109" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K109" t="s" s="2">
+      <c r="L109" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L109" t="s" s="2">
+      <c r="M109" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M109" t="s" s="2">
+      <c r="N109" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>76</v>
@@ -14990,7 +14987,7 @@
         <v>165</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AC109" t="s" s="2">
         <v>76</v>
@@ -14999,7 +14996,7 @@
         <v>132</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF109" t="s" s="2">
         <v>74</v>
@@ -15014,16 +15011,16 @@
         <v>94</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK109" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK109" t="s" s="2">
+      <c r="AL109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM109" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>76</v>
@@ -15031,7 +15028,7 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B110" s="2"/>
       <c r="C110" t="s" s="2">
@@ -15143,7 +15140,7 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" t="s" s="2">
@@ -15257,7 +15254,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" t="s" s="2">
@@ -15283,10 +15280,10 @@
         <v>102</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -15316,52 +15313,52 @@
         <v>187</v>
       </c>
       <c r="X112" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y112" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y112" t="s" s="2">
+      <c r="Z112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE112" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE112" t="s" s="2">
+      <c r="AF112" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH112" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ112" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>76</v>
@@ -15369,7 +15366,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B113" s="2"/>
       <c r="C113" t="s" s="2">
@@ -15395,16 +15392,16 @@
         <v>172</v>
       </c>
       <c r="K113" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L113" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L113" t="s" s="2">
+      <c r="M113" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>76</v>
@@ -15453,7 +15450,7 @@
         <v>76</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF113" t="s" s="2">
         <v>74</v>
@@ -15468,16 +15465,16 @@
         <v>94</v>
       </c>
       <c r="AJ113" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM113" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>76</v>
@@ -15485,7 +15482,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B114" s="2"/>
       <c r="C114" t="s" s="2">
@@ -15511,16 +15508,16 @@
         <v>102</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L114" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="M114" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O114" t="s" s="2">
         <v>76</v>
@@ -15549,25 +15546,25 @@
       </c>
       <c r="X114" s="2"/>
       <c r="Y114" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE114" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>74</v>
@@ -15591,7 +15588,7 @@
         <v>76</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>76</v>
@@ -15599,7 +15596,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B115" s="2"/>
       <c r="C115" t="s" s="2">
@@ -15622,16 +15619,16 @@
         <v>83</v>
       </c>
       <c r="J115" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K115" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K115" t="s" s="2">
+      <c r="L115" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L115" t="s" s="2">
+      <c r="M115" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
@@ -15681,7 +15678,7 @@
         <v>76</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF115" t="s" s="2">
         <v>74</v>
@@ -15713,7 +15710,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" t="s" s="2">
@@ -15739,10 +15736,10 @@
         <v>282</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
@@ -15793,7 +15790,7 @@
         <v>76</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF116" t="s" s="2">
         <v>74</v>
@@ -15825,10 +15822,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C117" t="s" s="2">
         <v>76</v>
@@ -15850,19 +15847,19 @@
         <v>83</v>
       </c>
       <c r="J117" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K117" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K117" t="s" s="2">
+      <c r="L117" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M117" t="s" s="2">
+      <c r="N117" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O117" t="s" s="2">
         <v>76</v>
@@ -15911,7 +15908,7 @@
         <v>76</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF117" t="s" s="2">
         <v>74</v>
@@ -15926,16 +15923,16 @@
         <v>94</v>
       </c>
       <c r="AJ117" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK117" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK117" t="s" s="2">
+      <c r="AL117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM117" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>76</v>
@@ -15943,7 +15940,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B118" s="2"/>
       <c r="C118" t="s" s="2">
@@ -16055,7 +16052,7 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B119" s="2"/>
       <c r="C119" t="s" s="2">
@@ -16169,7 +16166,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" t="s" s="2">
@@ -16195,10 +16192,10 @@
         <v>102</v>
       </c>
       <c r="K120" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L120" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
@@ -16210,7 +16207,7 @@
         <v>76</v>
       </c>
       <c r="R120" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S120" t="s" s="2">
         <v>76</v>
@@ -16228,52 +16225,52 @@
         <v>187</v>
       </c>
       <c r="X120" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y120" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y120" t="s" s="2">
+      <c r="Z120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE120" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE120" t="s" s="2">
+      <c r="AF120" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH120" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ120" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM120" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>76</v>
@@ -16281,7 +16278,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B121" s="2"/>
       <c r="C121" t="s" s="2">
@@ -16307,16 +16304,16 @@
         <v>172</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O121" t="s" s="2">
         <v>76</v>
@@ -16365,7 +16362,7 @@
         <v>76</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF121" t="s" s="2">
         <v>74</v>
@@ -16380,16 +16377,16 @@
         <v>94</v>
       </c>
       <c r="AJ121" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM121" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>76</v>
@@ -16397,7 +16394,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B122" s="2"/>
       <c r="C122" t="s" s="2">
@@ -16423,16 +16420,16 @@
         <v>102</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>76</v>
@@ -16442,7 +16439,7 @@
         <v>76</v>
       </c>
       <c r="R122" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>76</v>
@@ -16461,25 +16458,25 @@
       </c>
       <c r="X122" s="2"/>
       <c r="Y122" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE122" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF122" t="s" s="2">
         <v>74</v>
@@ -16503,7 +16500,7 @@
         <v>76</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>76</v>
@@ -16511,7 +16508,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B123" s="2"/>
       <c r="C123" t="s" s="2">
@@ -16534,16 +16531,16 @@
         <v>83</v>
       </c>
       <c r="J123" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K123" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K123" t="s" s="2">
+      <c r="L123" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L123" t="s" s="2">
+      <c r="M123" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
@@ -16593,7 +16590,7 @@
         <v>76</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF123" t="s" s="2">
         <v>74</v>
@@ -16625,7 +16622,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B124" s="2"/>
       <c r="C124" t="s" s="2">
@@ -16651,10 +16648,10 @@
         <v>282</v>
       </c>
       <c r="K124" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L124" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
@@ -16705,7 +16702,7 @@
         <v>76</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF124" t="s" s="2">
         <v>74</v>
@@ -16737,10 +16734,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>76</v>
@@ -16762,19 +16759,19 @@
         <v>83</v>
       </c>
       <c r="J125" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K125" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K125" t="s" s="2">
+      <c r="L125" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L125" t="s" s="2">
+      <c r="M125" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M125" t="s" s="2">
+      <c r="N125" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>76</v>
@@ -16823,7 +16820,7 @@
         <v>76</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF125" t="s" s="2">
         <v>74</v>
@@ -16838,16 +16835,16 @@
         <v>94</v>
       </c>
       <c r="AJ125" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK125" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK125" t="s" s="2">
+      <c r="AL125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM125" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>76</v>
@@ -16855,7 +16852,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B126" s="2"/>
       <c r="C126" t="s" s="2">
@@ -16967,7 +16964,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B127" s="2"/>
       <c r="C127" t="s" s="2">
@@ -17081,7 +17078,7 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B128" s="2"/>
       <c r="C128" t="s" s="2">
@@ -17107,10 +17104,10 @@
         <v>102</v>
       </c>
       <c r="K128" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L128" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -17122,7 +17119,7 @@
         <v>76</v>
       </c>
       <c r="R128" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>76</v>
@@ -17140,52 +17137,52 @@
         <v>187</v>
       </c>
       <c r="X128" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y128" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y128" t="s" s="2">
+      <c r="Z128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE128" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE128" t="s" s="2">
+      <c r="AF128" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH128" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ128" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM128" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>76</v>
@@ -17193,7 +17190,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B129" s="2"/>
       <c r="C129" t="s" s="2">
@@ -17219,16 +17216,16 @@
         <v>172</v>
       </c>
       <c r="K129" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L129" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L129" t="s" s="2">
+      <c r="M129" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M129" t="s" s="2">
+      <c r="N129" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O129" t="s" s="2">
         <v>76</v>
@@ -17277,7 +17274,7 @@
         <v>76</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF129" t="s" s="2">
         <v>74</v>
@@ -17292,16 +17289,16 @@
         <v>94</v>
       </c>
       <c r="AJ129" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM129" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>76</v>
@@ -17309,7 +17306,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B130" s="2"/>
       <c r="C130" t="s" s="2">
@@ -17335,16 +17332,16 @@
         <v>102</v>
       </c>
       <c r="K130" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L130" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L130" t="s" s="2">
+      <c r="M130" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M130" t="s" s="2">
+      <c r="N130" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O130" t="s" s="2">
         <v>76</v>
@@ -17354,7 +17351,7 @@
         <v>76</v>
       </c>
       <c r="R130" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>76</v>
@@ -17373,25 +17370,25 @@
       </c>
       <c r="X130" s="2"/>
       <c r="Y130" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE130" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF130" t="s" s="2">
         <v>74</v>
@@ -17415,7 +17412,7 @@
         <v>76</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>76</v>
@@ -17423,7 +17420,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B131" s="2"/>
       <c r="C131" t="s" s="2">
@@ -17446,16 +17443,16 @@
         <v>83</v>
       </c>
       <c r="J131" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K131" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K131" t="s" s="2">
+      <c r="L131" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L131" t="s" s="2">
+      <c r="M131" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
@@ -17466,7 +17463,7 @@
         <v>76</v>
       </c>
       <c r="R131" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>76</v>
@@ -17505,7 +17502,7 @@
         <v>76</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF131" t="s" s="2">
         <v>74</v>
@@ -17537,7 +17534,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" t="s" s="2">
@@ -17563,10 +17560,10 @@
         <v>282</v>
       </c>
       <c r="K132" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L132" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
@@ -17617,7 +17614,7 @@
         <v>76</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF132" t="s" s="2">
         <v>74</v>
@@ -17649,10 +17646,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C133" t="s" s="2">
         <v>76</v>
@@ -17674,19 +17671,19 @@
         <v>83</v>
       </c>
       <c r="J133" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K133" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K133" t="s" s="2">
+      <c r="L133" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L133" t="s" s="2">
+      <c r="M133" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M133" t="s" s="2">
+      <c r="N133" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O133" t="s" s="2">
         <v>76</v>
@@ -17735,7 +17732,7 @@
         <v>76</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF133" t="s" s="2">
         <v>74</v>
@@ -17750,16 +17747,16 @@
         <v>94</v>
       </c>
       <c r="AJ133" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK133" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK133" t="s" s="2">
+      <c r="AL133" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM133" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>76</v>
@@ -17767,7 +17764,7 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B134" s="2"/>
       <c r="C134" t="s" s="2">
@@ -17879,7 +17876,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" t="s" s="2">
@@ -17993,7 +17990,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B136" s="2"/>
       <c r="C136" t="s" s="2">
@@ -18019,10 +18016,10 @@
         <v>102</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
@@ -18034,7 +18031,7 @@
         <v>76</v>
       </c>
       <c r="R136" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S136" t="s" s="2">
         <v>76</v>
@@ -18052,52 +18049,52 @@
         <v>187</v>
       </c>
       <c r="X136" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y136" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y136" t="s" s="2">
+      <c r="Z136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE136" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE136" t="s" s="2">
+      <c r="AF136" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH136" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ136" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM136" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>76</v>
@@ -18105,7 +18102,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" t="s" s="2">
@@ -18131,16 +18128,16 @@
         <v>172</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L137" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="M137" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O137" t="s" s="2">
         <v>76</v>
@@ -18189,7 +18186,7 @@
         <v>76</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF137" t="s" s="2">
         <v>74</v>
@@ -18204,16 +18201,16 @@
         <v>94</v>
       </c>
       <c r="AJ137" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM137" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>76</v>
@@ -18221,7 +18218,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B138" s="2"/>
       <c r="C138" t="s" s="2">
@@ -18247,16 +18244,16 @@
         <v>102</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O138" t="s" s="2">
         <v>76</v>
@@ -18266,7 +18263,7 @@
         <v>76</v>
       </c>
       <c r="R138" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="S138" t="s" s="2">
         <v>76</v>
@@ -18285,25 +18282,25 @@
       </c>
       <c r="X138" s="2"/>
       <c r="Y138" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE138" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF138" t="s" s="2">
         <v>74</v>
@@ -18327,7 +18324,7 @@
         <v>76</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>76</v>
@@ -18335,7 +18332,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B139" s="2"/>
       <c r="C139" t="s" s="2">
@@ -18358,16 +18355,16 @@
         <v>83</v>
       </c>
       <c r="J139" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K139" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K139" t="s" s="2">
+      <c r="L139" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L139" t="s" s="2">
+      <c r="M139" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" t="s" s="2">
@@ -18378,7 +18375,7 @@
         <v>76</v>
       </c>
       <c r="R139" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>76</v>
@@ -18417,7 +18414,7 @@
         <v>76</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF139" t="s" s="2">
         <v>74</v>
@@ -18449,7 +18446,7 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B140" s="2"/>
       <c r="C140" t="s" s="2">
@@ -18475,10 +18472,10 @@
         <v>282</v>
       </c>
       <c r="K140" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L140" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
@@ -18529,7 +18526,7 @@
         <v>76</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF140" t="s" s="2">
         <v>74</v>
@@ -18561,10 +18558,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C141" t="s" s="2">
         <v>76</v>
@@ -18586,19 +18583,19 @@
         <v>83</v>
       </c>
       <c r="J141" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K141" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K141" t="s" s="2">
+      <c r="L141" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M141" t="s" s="2">
+      <c r="N141" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>76</v>
@@ -18647,7 +18644,7 @@
         <v>76</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF141" t="s" s="2">
         <v>74</v>
@@ -18662,16 +18659,16 @@
         <v>94</v>
       </c>
       <c r="AJ141" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK141" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK141" t="s" s="2">
+      <c r="AL141" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>76</v>
@@ -18679,7 +18676,7 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B142" s="2"/>
       <c r="C142" t="s" s="2">
@@ -18791,7 +18788,7 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B143" s="2"/>
       <c r="C143" t="s" s="2">
@@ -18905,7 +18902,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B144" s="2"/>
       <c r="C144" t="s" s="2">
@@ -18931,10 +18928,10 @@
         <v>102</v>
       </c>
       <c r="K144" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L144" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
@@ -18946,7 +18943,7 @@
         <v>76</v>
       </c>
       <c r="R144" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>76</v>
@@ -18964,52 +18961,52 @@
         <v>187</v>
       </c>
       <c r="X144" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y144" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y144" t="s" s="2">
+      <c r="Z144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE144" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE144" t="s" s="2">
+      <c r="AF144" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH144" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ144" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL144" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM144" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>76</v>
@@ -19017,7 +19014,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B145" s="2"/>
       <c r="C145" t="s" s="2">
@@ -19043,16 +19040,16 @@
         <v>172</v>
       </c>
       <c r="K145" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L145" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L145" t="s" s="2">
+      <c r="M145" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M145" t="s" s="2">
+      <c r="N145" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O145" t="s" s="2">
         <v>76</v>
@@ -19101,7 +19098,7 @@
         <v>76</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF145" t="s" s="2">
         <v>74</v>
@@ -19116,16 +19113,16 @@
         <v>94</v>
       </c>
       <c r="AJ145" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL145" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM145" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL145" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM145" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>76</v>
@@ -19133,7 +19130,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B146" s="2"/>
       <c r="C146" t="s" s="2">
@@ -19159,16 +19156,16 @@
         <v>102</v>
       </c>
       <c r="K146" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L146" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L146" t="s" s="2">
+      <c r="M146" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M146" t="s" s="2">
+      <c r="N146" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N146" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O146" t="s" s="2">
         <v>76</v>
@@ -19178,7 +19175,7 @@
         <v>76</v>
       </c>
       <c r="R146" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S146" t="s" s="2">
         <v>76</v>
@@ -19197,25 +19194,25 @@
       </c>
       <c r="X146" s="2"/>
       <c r="Y146" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE146" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF146" t="s" s="2">
         <v>74</v>
@@ -19239,7 +19236,7 @@
         <v>76</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>76</v>
@@ -19247,7 +19244,7 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B147" s="2"/>
       <c r="C147" t="s" s="2">
@@ -19270,16 +19267,16 @@
         <v>83</v>
       </c>
       <c r="J147" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K147" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K147" t="s" s="2">
+      <c r="L147" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
@@ -19329,7 +19326,7 @@
         <v>76</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF147" t="s" s="2">
         <v>74</v>
@@ -19361,7 +19358,7 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B148" s="2"/>
       <c r="C148" t="s" s="2">
@@ -19387,10 +19384,10 @@
         <v>282</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L148" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -19441,7 +19438,7 @@
         <v>76</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF148" t="s" s="2">
         <v>74</v>
@@ -19473,10 +19470,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>76</v>
@@ -19498,19 +19495,19 @@
         <v>83</v>
       </c>
       <c r="J149" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K149" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K149" t="s" s="2">
+      <c r="L149" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L149" t="s" s="2">
+      <c r="M149" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O149" t="s" s="2">
         <v>76</v>
@@ -19559,7 +19556,7 @@
         <v>76</v>
       </c>
       <c r="AE149" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF149" t="s" s="2">
         <v>74</v>
@@ -19574,16 +19571,16 @@
         <v>94</v>
       </c>
       <c r="AJ149" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK149" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK149" t="s" s="2">
+      <c r="AL149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>76</v>
@@ -19591,7 +19588,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B150" s="2"/>
       <c r="C150" t="s" s="2">
@@ -19703,7 +19700,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B151" s="2"/>
       <c r="C151" t="s" s="2">
@@ -19817,7 +19814,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B152" s="2"/>
       <c r="C152" t="s" s="2">
@@ -19843,10 +19840,10 @@
         <v>102</v>
       </c>
       <c r="K152" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L152" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L152" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -19858,7 +19855,7 @@
         <v>76</v>
       </c>
       <c r="R152" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>76</v>
@@ -19876,52 +19873,52 @@
         <v>187</v>
       </c>
       <c r="X152" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y152" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y152" t="s" s="2">
+      <c r="Z152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE152" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE152" t="s" s="2">
+      <c r="AF152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH152" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG152" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH152" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ152" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL152" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM152" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL152" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM152" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>76</v>
@@ -19929,7 +19926,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B153" s="2"/>
       <c r="C153" t="s" s="2">
@@ -19955,16 +19952,16 @@
         <v>172</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O153" t="s" s="2">
         <v>76</v>
@@ -20013,7 +20010,7 @@
         <v>76</v>
       </c>
       <c r="AE153" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF153" t="s" s="2">
         <v>74</v>
@@ -20028,16 +20025,16 @@
         <v>94</v>
       </c>
       <c r="AJ153" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK153" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL153" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM153" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL153" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM153" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>76</v>
@@ -20045,7 +20042,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B154" s="2"/>
       <c r="C154" t="s" s="2">
@@ -20071,16 +20068,16 @@
         <v>102</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M154" t="s" s="2">
+      <c r="N154" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O154" t="s" s="2">
         <v>76</v>
@@ -20090,7 +20087,7 @@
         <v>76</v>
       </c>
       <c r="R154" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="S154" t="s" s="2">
         <v>76</v>
@@ -20109,25 +20106,25 @@
       </c>
       <c r="X154" s="2"/>
       <c r="Y154" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE154" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD154" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE154" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF154" t="s" s="2">
         <v>74</v>
@@ -20151,7 +20148,7 @@
         <v>76</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN154" t="s" s="2">
         <v>76</v>
@@ -20159,7 +20156,7 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B155" s="2"/>
       <c r="C155" t="s" s="2">
@@ -20182,16 +20179,16 @@
         <v>83</v>
       </c>
       <c r="J155" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K155" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K155" t="s" s="2">
+      <c r="L155" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L155" t="s" s="2">
+      <c r="M155" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M155" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
@@ -20241,7 +20238,7 @@
         <v>76</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF155" t="s" s="2">
         <v>74</v>
@@ -20273,7 +20270,7 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B156" s="2"/>
       <c r="C156" t="s" s="2">
@@ -20299,10 +20296,10 @@
         <v>282</v>
       </c>
       <c r="K156" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L156" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L156" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -20353,7 +20350,7 @@
         <v>76</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF156" t="s" s="2">
         <v>74</v>
@@ -20385,10 +20382,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>76</v>
@@ -20410,19 +20407,19 @@
         <v>83</v>
       </c>
       <c r="J157" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="K157" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="K157" t="s" s="2">
+      <c r="L157" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="L157" t="s" s="2">
+      <c r="M157" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="O157" t="s" s="2">
         <v>76</v>
@@ -20471,7 +20468,7 @@
         <v>76</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AF157" t="s" s="2">
         <v>74</v>
@@ -20486,16 +20483,16 @@
         <v>94</v>
       </c>
       <c r="AJ157" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK157" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AK157" t="s" s="2">
+      <c r="AL157" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM157" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="AL157" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM157" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>76</v>
@@ -20503,7 +20500,7 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B158" s="2"/>
       <c r="C158" t="s" s="2">
@@ -20615,7 +20612,7 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B159" s="2"/>
       <c r="C159" t="s" s="2">
@@ -20727,10 +20724,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>76</v>
@@ -20752,13 +20749,13 @@
         <v>76</v>
       </c>
       <c r="J160" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="K160" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="K160" t="s" s="2">
-        <v>465</v>
-      </c>
       <c r="L160" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
@@ -20841,7 +20838,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B161" s="2"/>
       <c r="C161" t="s" s="2">
@@ -20867,10 +20864,10 @@
         <v>102</v>
       </c>
       <c r="K161" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="L161" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="L161" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
@@ -20882,7 +20879,7 @@
         <v>76</v>
       </c>
       <c r="R161" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="S161" t="s" s="2">
         <v>76</v>
@@ -20900,52 +20897,52 @@
         <v>187</v>
       </c>
       <c r="X161" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Y161" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Y161" t="s" s="2">
+      <c r="Z161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE161" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE161" t="s" s="2">
+      <c r="AF161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH161" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AF161" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG161" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH161" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ161" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL161" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM161" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AK161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL161" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM161" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>76</v>
@@ -20953,7 +20950,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B162" s="2"/>
       <c r="C162" t="s" s="2">
@@ -20979,16 +20976,16 @@
         <v>172</v>
       </c>
       <c r="K162" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L162" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L162" t="s" s="2">
+      <c r="M162" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O162" t="s" s="2">
         <v>76</v>
@@ -21037,7 +21034,7 @@
         <v>76</v>
       </c>
       <c r="AE162" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AF162" t="s" s="2">
         <v>74</v>
@@ -21052,16 +21049,16 @@
         <v>94</v>
       </c>
       <c r="AJ162" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL162" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM162" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="AK162" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL162" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM162" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>76</v>
@@ -21069,7 +21066,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B163" s="2"/>
       <c r="C163" t="s" s="2">
@@ -21095,16 +21092,16 @@
         <v>102</v>
       </c>
       <c r="K163" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L163" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L163" t="s" s="2">
+      <c r="M163" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M163" t="s" s="2">
+      <c r="N163" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="O163" t="s" s="2">
         <v>76</v>
@@ -21114,7 +21111,7 @@
         <v>76</v>
       </c>
       <c r="R163" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="S163" t="s" s="2">
         <v>76</v>
@@ -21133,25 +21130,25 @@
       </c>
       <c r="X163" s="2"/>
       <c r="Y163" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE163" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="Z163" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA163" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB163" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC163" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD163" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE163" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AF163" t="s" s="2">
         <v>74</v>
@@ -21175,7 +21172,7 @@
         <v>76</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>76</v>
@@ -21183,7 +21180,7 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B164" s="2"/>
       <c r="C164" t="s" s="2">
@@ -21206,16 +21203,16 @@
         <v>83</v>
       </c>
       <c r="J164" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="K164" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="K164" t="s" s="2">
+      <c r="L164" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L164" t="s" s="2">
+      <c r="M164" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="M164" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
@@ -21265,7 +21262,7 @@
         <v>76</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AF164" t="s" s="2">
         <v>74</v>
@@ -21297,7 +21294,7 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B165" s="2"/>
       <c r="C165" t="s" s="2">
@@ -21323,10 +21320,10 @@
         <v>282</v>
       </c>
       <c r="K165" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L165" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="L165" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
@@ -21377,7 +21374,7 @@
         <v>76</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AF165" t="s" s="2">
         <v>74</v>
@@ -21409,7 +21406,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B166" s="2"/>
       <c r="C166" t="s" s="2">
@@ -21435,16 +21432,16 @@
         <v>102</v>
       </c>
       <c r="K166" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L166" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L166" t="s" s="2">
+      <c r="M166" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="M166" t="s" s="2">
+      <c r="N166" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="O166" t="s" s="2">
         <v>76</v>
@@ -21472,11 +21469,11 @@
         <v>187</v>
       </c>
       <c r="X166" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Y166" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Y166" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="Z166" t="s" s="2">
         <v>76</v>
       </c>
@@ -21493,7 +21490,7 @@
         <v>76</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AF166" t="s" s="2">
         <v>74</v>
@@ -21508,16 +21505,16 @@
         <v>94</v>
       </c>
       <c r="AJ166" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AK166" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AK166" t="s" s="2">
+      <c r="AL166" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM166" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="AL166" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM166" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>76</v>
@@ -21525,7 +21522,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B167" s="2"/>
       <c r="C167" t="s" s="2">
@@ -21548,19 +21545,19 @@
         <v>83</v>
       </c>
       <c r="J167" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="K167" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="K167" t="s" s="2">
+      <c r="L167" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L167" t="s" s="2">
+      <c r="M167" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M167" t="s" s="2">
+      <c r="N167" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O167" t="s" s="2">
         <v>76</v>
@@ -21609,7 +21606,7 @@
         <v>76</v>
       </c>
       <c r="AE167" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AF167" t="s" s="2">
         <v>74</v>
@@ -21624,24 +21621,24 @@
         <v>94</v>
       </c>
       <c r="AJ167" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AK167" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="AK167" t="s" s="2">
+      <c r="AL167" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM167" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="AL167" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM167" t="s" s="2">
+      <c r="AN167" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN167" t="s" s="2">
-        <v>485</v>
       </c>
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B168" s="2"/>
       <c r="C168" t="s" s="2">
@@ -21664,19 +21661,19 @@
         <v>83</v>
       </c>
       <c r="J168" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="K168" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="K168" t="s" s="2">
+      <c r="L168" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="L168" t="s" s="2">
+      <c r="M168" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M168" t="s" s="2">
+      <c r="N168" t="s" s="2">
         <v>490</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>491</v>
       </c>
       <c r="O168" t="s" s="2">
         <v>76</v>
@@ -21725,7 +21722,7 @@
         <v>76</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AF168" t="s" s="2">
         <v>74</v>
@@ -21740,7 +21737,7 @@
         <v>94</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>176</v>
@@ -21749,7 +21746,7 @@
         <v>76</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>76</v>
@@ -21757,7 +21754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B169" s="2"/>
       <c r="C169" t="s" s="2">
@@ -21780,19 +21777,19 @@
         <v>76</v>
       </c>
       <c r="J169" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="K169" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="K169" t="s" s="2">
+      <c r="L169" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L169" t="s" s="2">
+      <c r="M169" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M169" t="s" s="2">
+      <c r="N169" t="s" s="2">
         <v>498</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>499</v>
       </c>
       <c r="O169" t="s" s="2">
         <v>76</v>
@@ -21841,7 +21838,7 @@
         <v>76</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AF169" t="s" s="2">
         <v>74</v>
@@ -21856,16 +21853,16 @@
         <v>94</v>
       </c>
       <c r="AJ169" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL169" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM169" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AK169" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AL169" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM169" t="s" s="2">
-        <v>501</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>76</v>
@@ -21873,7 +21870,7 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B170" s="2"/>
       <c r="C170" t="s" s="2">
@@ -21899,14 +21896,14 @@
         <v>193</v>
       </c>
       <c r="K170" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="L170" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="L170" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="O170" t="s" s="2">
         <v>76</v>
@@ -21931,14 +21928,14 @@
         <v>76</v>
       </c>
       <c r="W170" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="X170" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="X170" t="s" s="2">
+      <c r="Y170" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="Y170" t="s" s="2">
-        <v>508</v>
-      </c>
       <c r="Z170" t="s" s="2">
         <v>76</v>
       </c>
@@ -21955,7 +21952,7 @@
         <v>76</v>
       </c>
       <c r="AE170" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AF170" t="s" s="2">
         <v>74</v>
@@ -21970,16 +21967,16 @@
         <v>94</v>
       </c>
       <c r="AJ170" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AK170" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="AK170" t="s" s="2">
+      <c r="AL170" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM170" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="AL170" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM170" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>76</v>
@@ -21987,7 +21984,7 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B171" s="2"/>
       <c r="C171" t="s" s="2">
@@ -22010,19 +22007,19 @@
         <v>76</v>
       </c>
       <c r="J171" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="K171" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="K171" t="s" s="2">
+      <c r="L171" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="L171" t="s" s="2">
+      <c r="M171" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="M171" t="s" s="2">
+      <c r="N171" t="s" s="2">
         <v>516</v>
-      </c>
-      <c r="N171" t="s" s="2">
-        <v>517</v>
       </c>
       <c r="O171" t="s" s="2">
         <v>76</v>
@@ -22071,7 +22068,7 @@
         <v>76</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AF171" t="s" s="2">
         <v>74</v>
@@ -22086,7 +22083,7 @@
         <v>94</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>176</v>
@@ -22095,7 +22092,7 @@
         <v>76</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>76</v>
@@ -22103,7 +22100,7 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B172" s="2"/>
       <c r="C172" t="s" s="2">
@@ -22126,19 +22123,19 @@
         <v>76</v>
       </c>
       <c r="J172" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="K172" t="s" s="2">
         <v>521</v>
       </c>
-      <c r="K172" t="s" s="2">
+      <c r="L172" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L172" t="s" s="2">
+      <c r="M172" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M172" t="s" s="2">
+      <c r="N172" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="N172" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="O172" t="s" s="2">
         <v>76</v>
@@ -22187,7 +22184,7 @@
         <v>76</v>
       </c>
       <c r="AE172" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AF172" t="s" s="2">
         <v>74</v>
@@ -22202,7 +22199,7 @@
         <v>94</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>176</v>
@@ -22211,7 +22208,7 @@
         <v>76</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>76</v>
@@ -22219,7 +22216,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" t="s" s="2">
@@ -22242,19 +22239,19 @@
         <v>76</v>
       </c>
       <c r="J173" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="K173" t="s" s="2">
         <v>529</v>
       </c>
-      <c r="K173" t="s" s="2">
+      <c r="L173" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="L173" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O173" t="s" s="2">
         <v>76</v>
@@ -22303,7 +22300,7 @@
         <v>76</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AF173" t="s" s="2">
         <v>74</v>
@@ -22315,10 +22312,10 @@
         <v>76</v>
       </c>
       <c r="AI173" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AJ173" t="s" s="2">
         <v>533</v>
-      </c>
-      <c r="AJ173" t="s" s="2">
-        <v>534</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>176</v>
@@ -22335,7 +22332,7 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" t="s" s="2">
@@ -22447,7 +22444,7 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B175" s="2"/>
       <c r="C175" t="s" s="2">
@@ -22557,10 +22554,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B176" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>76</v>
@@ -22582,13 +22579,13 @@
         <v>76</v>
       </c>
       <c r="J176" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="K176" t="s" s="2">
         <v>538</v>
       </c>
-      <c r="K176" t="s" s="2">
+      <c r="L176" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="L176" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
@@ -22671,11 +22668,11 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -22697,10 +22694,10 @@
         <v>128</v>
       </c>
       <c r="K177" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L177" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="L177" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>156</v>
@@ -22755,7 +22752,7 @@
         <v>76</v>
       </c>
       <c r="AE177" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AF177" t="s" s="2">
         <v>74</v>
@@ -22787,7 +22784,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B178" s="2"/>
       <c r="C178" t="s" s="2">
@@ -22813,14 +22810,14 @@
         <v>193</v>
       </c>
       <c r="K178" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L178" t="s" s="2">
         <v>547</v>
-      </c>
-      <c r="L178" t="s" s="2">
-        <v>548</v>
       </c>
       <c r="M178" s="2"/>
       <c r="N178" t="s" s="2">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="O178" t="s" s="2">
         <v>76</v>
@@ -22848,11 +22845,11 @@
         <v>187</v>
       </c>
       <c r="X178" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Y178" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="Y178" t="s" s="2">
-        <v>551</v>
-      </c>
       <c r="Z178" t="s" s="2">
         <v>76</v>
       </c>
@@ -22869,7 +22866,7 @@
         <v>76</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="AF178" t="s" s="2">
         <v>74</v>
@@ -22884,7 +22881,7 @@
         <v>94</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>176</v>
@@ -22893,7 +22890,7 @@
         <v>76</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>76</v>
@@ -22901,7 +22898,7 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B179" s="2"/>
       <c r="C179" t="s" s="2">
@@ -23013,7 +23010,7 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B180" s="2"/>
       <c r="C180" t="s" s="2">
@@ -23127,7 +23124,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B181" s="2"/>
       <c r="C181" t="s" s="2">
@@ -23243,7 +23240,7 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B182" s="2"/>
       <c r="C182" t="s" s="2">
@@ -23355,7 +23352,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" t="s" s="2">
@@ -23469,7 +23466,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B184" s="2"/>
       <c r="C184" t="s" s="2">
@@ -23495,13 +23492,13 @@
         <v>96</v>
       </c>
       <c r="K184" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L184" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L184" t="s" s="2">
+      <c r="M184" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M184" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N184" t="s" s="2">
         <v>224</v>
@@ -23585,7 +23582,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B185" s="2"/>
       <c r="C185" t="s" s="2">
@@ -23699,7 +23696,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B186" s="2"/>
       <c r="C186" t="s" s="2">
@@ -23725,10 +23722,10 @@
         <v>102</v>
       </c>
       <c r="K186" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L186" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="L186" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="M186" s="2"/>
       <c r="N186" t="s" s="2">
@@ -23813,7 +23810,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B187" s="2"/>
       <c r="C187" t="s" s="2">
@@ -23839,10 +23836,10 @@
         <v>172</v>
       </c>
       <c r="K187" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L187" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="L187" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="M187" s="2"/>
       <c r="N187" t="s" s="2">
@@ -23927,7 +23924,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B188" s="2"/>
       <c r="C188" t="s" s="2">
@@ -24043,7 +24040,7 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B189" s="2"/>
       <c r="C189" t="s" s="2">
@@ -24159,7 +24156,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B190" s="2"/>
       <c r="C190" t="s" s="2">
@@ -24185,14 +24182,14 @@
         <v>310</v>
       </c>
       <c r="K190" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L190" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="L190" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="M190" s="2"/>
       <c r="N190" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="O190" t="s" s="2">
         <v>76</v>
@@ -24241,7 +24238,7 @@
         <v>76</v>
       </c>
       <c r="AE190" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AF190" t="s" s="2">
         <v>74</v>
@@ -24265,7 +24262,7 @@
         <v>76</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>76</v>
@@ -24273,7 +24270,7 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B191" s="2"/>
       <c r="C191" t="s" s="2">
@@ -24385,7 +24382,7 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B192" s="2"/>
       <c r="C192" t="s" s="2">
@@ -24499,7 +24496,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B193" s="2"/>
       <c r="C193" t="s" s="2">
@@ -24528,10 +24525,10 @@
         <v>324</v>
       </c>
       <c r="L193" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M193" t="s" s="2">
         <v>580</v>
-      </c>
-      <c r="M193" t="s" s="2">
-        <v>581</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>327</v>
@@ -24615,7 +24612,7 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B194" s="2"/>
       <c r="C194" t="s" s="2">
@@ -24731,7 +24728,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B195" s="2"/>
       <c r="C195" t="s" s="2">
@@ -24845,7 +24842,7 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B196" s="2"/>
       <c r="C196" t="s" s="2">
@@ -24957,7 +24954,7 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B197" s="2"/>
       <c r="C197" t="s" s="2">
@@ -25067,7 +25064,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>356</v>
@@ -25181,7 +25178,7 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" t="s" s="2">
@@ -25293,7 +25290,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" t="s" s="2">
@@ -25319,10 +25316,10 @@
         <v>172</v>
       </c>
       <c r="K200" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="L200" t="s" s="2">
         <v>588</v>
-      </c>
-      <c r="L200" t="s" s="2">
-        <v>589</v>
       </c>
       <c r="M200" t="s" s="2">
         <v>369</v>
@@ -25407,7 +25404,7 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B201" s="2"/>
       <c r="C201" t="s" s="2">
@@ -25519,7 +25516,7 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B202" s="2"/>
       <c r="C202" t="s" s="2">
@@ -25631,7 +25628,7 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B203" s="2"/>
       <c r="C203" t="s" s="2">
@@ -25745,7 +25742,7 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B204" s="2"/>
       <c r="C204" t="s" s="2">
@@ -25768,19 +25765,19 @@
         <v>76</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="K204" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L204" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="L204" t="s" s="2">
+      <c r="M204" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M204" t="s" s="2">
-        <v>596</v>
-      </c>
       <c r="N204" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="O204" t="s" s="2">
         <v>76</v>
@@ -25829,7 +25826,7 @@
         <v>76</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AF204" t="s" s="2">
         <v>74</v>
@@ -25844,7 +25841,7 @@
         <v>94</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>176</v>
@@ -25853,7 +25850,7 @@
         <v>76</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AN204" t="s" s="2">
         <v>76</v>
@@ -25861,7 +25858,7 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B205" s="2"/>
       <c r="C205" t="s" s="2">
@@ -25884,17 +25881,17 @@
         <v>76</v>
       </c>
       <c r="J205" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="K205" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="K205" t="s" s="2">
+      <c r="L205" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="L205" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="O205" t="s" s="2">
         <v>76</v>
@@ -25943,7 +25940,7 @@
         <v>76</v>
       </c>
       <c r="AE205" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AF205" t="s" s="2">
         <v>74</v>
@@ -25958,7 +25955,7 @@
         <v>94</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AK205" t="s" s="2">
         <v>176</v>
@@ -25967,7 +25964,7 @@
         <v>76</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AN205" t="s" s="2">
         <v>76</v>
@@ -25975,7 +25972,7 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B206" s="2"/>
       <c r="C206" t="s" s="2">
@@ -26001,14 +25998,14 @@
         <v>102</v>
       </c>
       <c r="K206" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L206" t="s" s="2">
         <v>606</v>
-      </c>
-      <c r="L206" t="s" s="2">
-        <v>607</v>
       </c>
       <c r="M206" s="2"/>
       <c r="N206" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="O206" t="s" s="2">
         <v>76</v>
@@ -26036,11 +26033,11 @@
         <v>187</v>
       </c>
       <c r="X206" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="Y206" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="Y206" t="s" s="2">
-        <v>472</v>
-      </c>
       <c r="Z206" t="s" s="2">
         <v>76</v>
       </c>
@@ -26057,7 +26054,7 @@
         <v>76</v>
       </c>
       <c r="AE206" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AF206" t="s" s="2">
         <v>74</v>
@@ -26072,7 +26069,7 @@
         <v>94</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AK206" t="s" s="2">
         <v>176</v>
@@ -26081,7 +26078,7 @@
         <v>76</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AN206" t="s" s="2">
         <v>76</v>
@@ -26089,7 +26086,7 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B207" s="2"/>
       <c r="C207" t="s" s="2">
@@ -26115,14 +26112,14 @@
         <v>289</v>
       </c>
       <c r="K207" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="L207" t="s" s="2">
         <v>611</v>
-      </c>
-      <c r="L207" t="s" s="2">
-        <v>612</v>
       </c>
       <c r="M207" s="2"/>
       <c r="N207" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="O207" t="s" s="2">
         <v>76</v>
@@ -26171,7 +26168,7 @@
         <v>76</v>
       </c>
       <c r="AE207" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AF207" t="s" s="2">
         <v>74</v>
@@ -26180,13 +26177,13 @@
         <v>82</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AJ207" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AK207" t="s" s="2">
         <v>176</v>
@@ -26195,7 +26192,7 @@
         <v>76</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>76</v>
@@ -26203,7 +26200,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B208" s="2"/>
       <c r="C208" t="s" s="2">
@@ -26229,10 +26226,10 @@
         <v>282</v>
       </c>
       <c r="K208" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L208" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="L208" t="s" s="2">
-        <v>619</v>
       </c>
       <c r="M208" s="2"/>
       <c r="N208" s="2"/>
@@ -26283,7 +26280,7 @@
         <v>76</v>
       </c>
       <c r="AE208" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AF208" t="s" s="2">
         <v>74</v>
@@ -26298,7 +26295,7 @@
         <v>94</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>176</v>
@@ -26315,7 +26312,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B209" s="2"/>
       <c r="C209" t="s" s="2">
@@ -26338,19 +26335,19 @@
         <v>76</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K209" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L209" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M209" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="L209" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="M209" t="s" s="2">
+      <c r="N209" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O209" t="s" s="2">
         <v>76</v>
@@ -26399,7 +26396,7 @@
         <v>76</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AF209" t="s" s="2">
         <v>74</v>
@@ -26414,10 +26411,10 @@
         <v>94</v>
       </c>
       <c r="AJ209" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AK209" t="s" s="2">
         <v>625</v>
-      </c>
-      <c r="AK209" t="s" s="2">
-        <v>626</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>76</v>
@@ -26431,7 +26428,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B210" s="2"/>
       <c r="C210" t="s" s="2">
@@ -26543,7 +26540,7 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B211" s="2"/>
       <c r="C211" t="s" s="2">
@@ -26657,11 +26654,11 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B212" s="2"/>
       <c r="C212" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26683,10 +26680,10 @@
         <v>128</v>
       </c>
       <c r="K212" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L212" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="L212" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="M212" t="s" s="2">
         <v>156</v>
@@ -26741,7 +26738,7 @@
         <v>76</v>
       </c>
       <c r="AE212" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AF212" t="s" s="2">
         <v>74</v>
@@ -26773,7 +26770,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B213" s="2"/>
       <c r="C213" t="s" s="2">
@@ -26799,16 +26796,16 @@
         <v>193</v>
       </c>
       <c r="K213" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="L213" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="L213" t="s" s="2">
+      <c r="M213" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M213" t="s" s="2">
+      <c r="N213" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="N213" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O213" t="s" s="2">
         <v>76</v>
@@ -26836,11 +26833,11 @@
         <v>187</v>
       </c>
       <c r="X213" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="Y213" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="Y213" t="s" s="2">
-        <v>636</v>
-      </c>
       <c r="Z213" t="s" s="2">
         <v>76</v>
       </c>
@@ -26857,7 +26854,7 @@
         <v>76</v>
       </c>
       <c r="AE213" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AF213" t="s" s="2">
         <v>82</v>
@@ -26872,16 +26869,16 @@
         <v>94</v>
       </c>
       <c r="AJ213" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AK213" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="AK213" t="s" s="2">
+      <c r="AL213" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM213" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="AL213" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM213" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>76</v>
@@ -26889,7 +26886,7 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B214" s="2"/>
       <c r="C214" t="s" s="2">
@@ -27001,7 +26998,7 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B215" s="2"/>
       <c r="C215" t="s" s="2">
@@ -27115,7 +27112,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B216" s="2"/>
       <c r="C216" t="s" s="2">
@@ -27231,7 +27228,7 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B217" s="2"/>
       <c r="C217" t="s" s="2">
@@ -27343,7 +27340,7 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B218" s="2"/>
       <c r="C218" t="s" s="2">
@@ -27457,7 +27454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B219" s="2"/>
       <c r="C219" t="s" s="2">
@@ -27483,13 +27480,13 @@
         <v>96</v>
       </c>
       <c r="K219" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="L219" t="s" s="2">
         <v>560</v>
       </c>
-      <c r="L219" t="s" s="2">
+      <c r="M219" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="M219" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="N219" t="s" s="2">
         <v>224</v>
@@ -27573,7 +27570,7 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B220" s="2"/>
       <c r="C220" t="s" s="2">
@@ -27687,7 +27684,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B221" s="2"/>
       <c r="C221" t="s" s="2">
@@ -27713,10 +27710,10 @@
         <v>102</v>
       </c>
       <c r="K221" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L221" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="L221" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="M221" s="2"/>
       <c r="N221" t="s" s="2">
@@ -27801,7 +27798,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B222" s="2"/>
       <c r="C222" t="s" s="2">
@@ -27827,10 +27824,10 @@
         <v>172</v>
       </c>
       <c r="K222" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="L222" t="s" s="2">
         <v>568</v>
-      </c>
-      <c r="L222" t="s" s="2">
-        <v>569</v>
       </c>
       <c r="M222" s="2"/>
       <c r="N222" t="s" s="2">
@@ -27915,7 +27912,7 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B223" s="2"/>
       <c r="C223" t="s" s="2">
@@ -28031,7 +28028,7 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B224" s="2"/>
       <c r="C224" t="s" s="2">
@@ -28147,7 +28144,7 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B225" s="2"/>
       <c r="C225" t="s" s="2">
@@ -28173,16 +28170,16 @@
         <v>248</v>
       </c>
       <c r="K225" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="L225" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="L225" t="s" s="2">
+      <c r="M225" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="M225" t="s" s="2">
+      <c r="N225" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="O225" t="s" s="2">
         <v>76</v>
@@ -28231,7 +28228,7 @@
         <v>76</v>
       </c>
       <c r="AE225" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AF225" t="s" s="2">
         <v>74</v>
@@ -28246,16 +28243,16 @@
         <v>94</v>
       </c>
       <c r="AJ225" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AK225" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="AK225" t="s" s="2">
+      <c r="AL225" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM225" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="AL225" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AM225" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="AN225" t="s" s="2">
         <v>76</v>
@@ -28263,11 +28260,11 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B226" s="2"/>
       <c r="C226" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28286,16 +28283,16 @@
         <v>76</v>
       </c>
       <c r="J226" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="K226" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="K226" t="s" s="2">
+      <c r="L226" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M226" t="s" s="2">
         <v>662</v>
-      </c>
-      <c r="L226" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="M226" t="s" s="2">
-        <v>663</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" t="s" s="2">
@@ -28345,7 +28342,7 @@
         <v>76</v>
       </c>
       <c r="AE226" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AF226" t="s" s="2">
         <v>74</v>
@@ -28360,7 +28357,7 @@
         <v>94</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AK226" t="s" s="2">
         <v>176</v>
@@ -28369,7 +28366,7 @@
         <v>76</v>
       </c>
       <c r="AM226" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AN226" t="s" s="2">
         <v>76</v>
@@ -28377,7 +28374,7 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B227" s="2"/>
       <c r="C227" t="s" s="2">
@@ -28489,7 +28486,7 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B228" s="2"/>
       <c r="C228" t="s" s="2">
@@ -28603,7 +28600,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B229" s="2"/>
       <c r="C229" t="s" s="2">
@@ -28629,13 +28626,13 @@
         <v>172</v>
       </c>
       <c r="K229" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="L229" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M229" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="L229" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M229" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="N229" s="2"/>
       <c r="O229" t="s" s="2">
@@ -28685,16 +28682,16 @@
         <v>76</v>
       </c>
       <c r="AE229" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="AF229" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AG229" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH229" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="AF229" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AG229" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH229" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>94</v>
@@ -28717,7 +28714,7 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B230" s="2"/>
       <c r="C230" t="s" s="2">
@@ -28743,13 +28740,13 @@
         <v>96</v>
       </c>
       <c r="K230" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="L230" t="s" s="2">
         <v>674</v>
       </c>
-      <c r="L230" t="s" s="2">
+      <c r="M230" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="M230" t="s" s="2">
-        <v>676</v>
       </c>
       <c r="N230" s="2"/>
       <c r="O230" t="s" s="2">
@@ -28775,31 +28772,31 @@
         <v>76</v>
       </c>
       <c r="W230" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="X230" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="Y230" t="s" s="2">
         <v>677</v>
       </c>
-      <c r="Y230" t="s" s="2">
+      <c r="Z230" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA230" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB230" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC230" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD230" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE230" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="Z230" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AA230" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB230" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC230" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD230" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE230" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="AF230" t="s" s="2">
         <v>74</v>
@@ -28831,7 +28828,7 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B231" s="2"/>
       <c r="C231" t="s" s="2">
@@ -28857,13 +28854,13 @@
         <v>160</v>
       </c>
       <c r="K231" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="L231" t="s" s="2">
         <v>681</v>
       </c>
-      <c r="L231" t="s" s="2">
+      <c r="M231" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="M231" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" t="s" s="2">
@@ -28913,7 +28910,7 @@
         <v>76</v>
       </c>
       <c r="AE231" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AF231" t="s" s="2">
         <v>74</v>
@@ -28928,7 +28925,7 @@
         <v>94</v>
       </c>
       <c r="AJ231" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AK231" t="s" s="2">
         <v>76</v>
@@ -28945,7 +28942,7 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B232" s="2"/>
       <c r="C232" t="s" s="2">
@@ -28971,13 +28968,13 @@
         <v>172</v>
       </c>
       <c r="K232" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="L232" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="L232" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="M232" t="s" s="2">
-        <v>688</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" t="s" s="2">
@@ -29027,7 +29024,7 @@
         <v>76</v>
       </c>
       <c r="AE232" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AF232" t="s" s="2">
         <v>74</v>
@@ -29059,7 +29056,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B233" s="2"/>
       <c r="C233" t="s" s="2">
@@ -29085,16 +29082,16 @@
         <v>289</v>
       </c>
       <c r="K233" t="s" s="2">
+        <v>690</v>
+      </c>
+      <c r="L233" t="s" s="2">
         <v>691</v>
       </c>
-      <c r="L233" t="s" s="2">
+      <c r="M233" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="M233" t="s" s="2">
+      <c r="N233" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="O233" t="s" s="2">
         <v>76</v>
@@ -29143,7 +29140,7 @@
         <v>76</v>
       </c>
       <c r="AE233" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="AF233" t="s" s="2">
         <v>74</v>
@@ -29158,10 +29155,10 @@
         <v>94</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AL233" t="s" s="2">
         <v>76</v>
@@ -29175,7 +29172,7 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B234" s="2"/>
       <c r="C234" t="s" s="2">
@@ -29198,19 +29195,19 @@
         <v>83</v>
       </c>
       <c r="J234" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="K234" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="L234" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="L234" t="s" s="2">
+      <c r="M234" t="s" s="2">
         <v>698</v>
       </c>
-      <c r="M234" t="s" s="2">
+      <c r="N234" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="N234" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="O234" t="s" s="2">
         <v>76</v>
@@ -29259,7 +29256,7 @@
         <v>76</v>
       </c>
       <c r="AE234" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="AF234" t="s" s="2">
         <v>74</v>
@@ -29274,7 +29271,7 @@
         <v>94</v>
       </c>
       <c r="AJ234" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AK234" t="s" s="2">
         <v>176</v>
@@ -29291,7 +29288,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B235" s="2"/>
       <c r="C235" t="s" s="2">
@@ -29403,7 +29400,7 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B236" s="2"/>
       <c r="C236" t="s" s="2">
@@ -29517,11 +29514,11 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B237" s="2"/>
       <c r="C237" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29543,10 +29540,10 @@
         <v>128</v>
       </c>
       <c r="K237" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="L237" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="M237" t="s" s="2">
         <v>156</v>
@@ -29601,7 +29598,7 @@
         <v>76</v>
       </c>
       <c r="AE237" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AF237" t="s" s="2">
         <v>74</v>
@@ -29633,7 +29630,7 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B238" s="2"/>
       <c r="C238" t="s" s="2">
@@ -29656,16 +29653,16 @@
         <v>83</v>
       </c>
       <c r="J238" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="K238" t="s" s="2">
         <v>706</v>
       </c>
-      <c r="K238" t="s" s="2">
+      <c r="L238" t="s" s="2">
         <v>707</v>
       </c>
-      <c r="L238" t="s" s="2">
+      <c r="M238" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" t="s" s="2">
@@ -29715,7 +29712,7 @@
         <v>76</v>
       </c>
       <c r="AE238" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AF238" t="s" s="2">
         <v>82</v>
@@ -29739,7 +29736,7 @@
         <v>76</v>
       </c>
       <c r="AM238" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AN238" t="s" s="2">
         <v>76</v>
@@ -29747,7 +29744,7 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B239" s="2"/>
       <c r="C239" t="s" s="2">
@@ -29773,10 +29770,10 @@
         <v>102</v>
       </c>
       <c r="K239" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="L239" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="M239" s="2"/>
       <c r="N239" s="2"/>
@@ -29806,11 +29803,11 @@
         <v>187</v>
       </c>
       <c r="X239" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="Y239" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="Y239" t="s" s="2">
-        <v>714</v>
-      </c>
       <c r="Z239" t="s" s="2">
         <v>76</v>
       </c>
@@ -29827,7 +29824,7 @@
         <v>76</v>
       </c>
       <c r="AE239" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AF239" t="s" s="2">
         <v>82</v>
@@ -29842,7 +29839,7 @@
         <v>94</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>176</v>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-PacienteLE.xlsx
+++ b/refs/heads/main/StructureDefinition-PacienteLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
